--- a/user.xlsx
+++ b/user.xlsx
@@ -5,11 +5,11 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\namw2\Documents\NetBeansProjects\exel_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\namw2\Documents\NetBeansProjects\University\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="25350" windowHeight="11100" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="17710" windowHeight="6280" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Sheet1" sheetId="1" r:id="rId4"/>
@@ -109,532 +109,532 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="176">
   <x:si>
+    <x:t>박은빈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신예원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최현진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서지민</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차은우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임효빈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김정호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전수연</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송다영</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임현아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김민석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장상호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박지원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정대현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이수진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정하늘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박수진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송미래</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박상훈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김지민</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김혜지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>황선미</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이소희</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장민수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서지수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전산학</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김동혁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박하늘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김나영</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이수민</x:t>
+  </x:si>
+  <x:si>
+    <x:t>윤정원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이지혜</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구세린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이다빈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최동현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강지훈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정민수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이영진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김동호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임윤아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박민경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김현우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>홍지은</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전해진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김수연</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최지혜</x:t>
+  </x:si>
+  <x:si>
+    <x:t>yuna.lim@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jihye.lee@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hyeji.kim@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>serin.gu@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jimin.seo@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sujin.lee@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dabin.lee@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jisoo.seo@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hyuna.lim@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sohee.lee@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jimin.kim@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BachelorEmployee</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 강서구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 성동구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 강동구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 양천구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 서초구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 서대문구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 중구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 도봉구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 은평구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 강남구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 마포구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 동대문구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 관악구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 종로구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S045</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 중랑구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>address</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 동작구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 용산구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 송파구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>email</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Major</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>number</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 금천구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 강북구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울 광진구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자공학</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화학공학</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>항공우주공학</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계공학</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Student</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Security_num</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClassEmployee</x:t>
+  </x:si>
+  <x:si>
+    <x:t>permission</x:t>
+  </x:si>
+  <x:si>
+    <x:t>password</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Professor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>minkyung.park@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>suyeon.jeon@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>donghyuk.kim@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jihoon.kang@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jiwon.park@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hyunwoo.kim@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>haejin.jeon@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dayoung.song@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nayoung.kim@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>minsu.jang@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jeongho.kim@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>youngjin.lee@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>yewon.shin@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hyunjin.choi@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sunmi.hwang@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jeongwon.yoon@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>eunbin.park@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hyobin.lim@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>daehyun.jung@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>minseok.kim@email.com</x:t>
+  </x:si>
+  <x:si>
     <x:t>jieun.hong@email.com</x:t>
   </x:si>
   <x:si>
+    <x:t>soomin.lee@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dongho.kim@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sanghun.park@email.com</x:t>
+  </x:si>
+  <x:si>
     <x:t>jihye.choi@email.com</x:t>
   </x:si>
   <x:si>
-    <x:t>donghyuk.kim@email.com</x:t>
+    <x:t>mirae.song@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>donghyun.choi@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>suyeon.kim@email.com</x:t>
   </x:si>
   <x:si>
     <x:t>sujin.park@email.com</x:t>
   </x:si>
   <x:si>
-    <x:t>soomin.lee@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>eunbin.park@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>minseok.kim@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>suyeon.jeon@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jihoon.kang@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dongho.kim@email.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>eunwoo.cha@email.com</x:t>
   </x:si>
   <x:si>
-    <x:t>yewon.shin@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jiwon.park@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hyobin.lim@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>daehyun.jung@email.com</x:t>
+    <x:t>haneul.jung@email.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sangho.jang@email.com</x:t>
   </x:si>
   <x:si>
     <x:t>haneul.park@email.com</x:t>
   </x:si>
   <x:si>
-    <x:t>haneul.jung@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>haejin.jeon@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nayoung.kim@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dayoung.song@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sunmi.hwang@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hyunwoo.kim@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>minkyung.park@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mirae.song@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jeongho.kim@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>suyeon.kim@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jeongwon.yoon@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sanghun.park@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>minsu.jang@email.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>minsu.jeong@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sangho.jang@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>donghyun.choi@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>youngjin.lee@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hyunjin.choi@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>차은우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박은빈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김민석</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박상훈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김혜지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임효빈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김지민</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서지민</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이수진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최현진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전수연</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송다영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신예원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임현아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박하늘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이소희</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김나영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>황선미</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이수민</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장민수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서지수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김동혁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강지훈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최동현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박민경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>홍지은</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김동호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>윤정원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최지혜</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구세린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김정호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정하늘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이다빈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이영진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정대현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김현우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정민수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전해진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송미래</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박수진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김수연</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임윤아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이지혜</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박지원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장상호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jimin.kim@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hyuna.lim@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>yuna.lim@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hyeji.kim@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jisoo.seo@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sujin.lee@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>serin.gu@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sohee.lee@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jihye.lee@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dabin.lee@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jimin.seo@email.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수업담당자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계공학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 강남구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학사담당자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 관악구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화학공학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전산학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 서초구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>항공우주공학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 마포구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 은평구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 도봉구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 양천구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 동대문구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 강동구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 성동구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 강서구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 금천구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 서대문구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 동작구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 중구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 강북구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 용산구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 송파구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G038</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S039</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자공학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 광진구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S045</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 중랑구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울 종로구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>address</x:t>
-  </x:si>
-  <x:si>
-    <x:t>email</x:t>
-  </x:si>
-  <x:si>
-    <x:t>number</x:t>
-  </x:si>
-  <x:si>
-    <x:t>grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Security_num</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Major</x:t>
-  </x:si>
-  <x:si>
-    <x:t>permission</x:t>
-  </x:si>
-  <x:si>
-    <x:t>id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>password</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1008,63 +1008,63 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>174</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I1" t="s">
-        <x:v>175</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>173</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>170</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11">
       <x:c r="A2" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E2" s="2">
         <x:v>1234567</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="I2" s="2">
         <x:v>1234567</x:v>
@@ -1078,28 +1078,28 @@
     </x:row>
     <x:row r="3" spans="1:10">
       <x:c r="A3" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>159</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E3" s="2">
         <x:v>2345678</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>159</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I3" s="2">
         <x:v>2345678</x:v>
@@ -1108,30 +1108,30 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:10">
+    <x:row r="4" spans="1:10" ht="32.75">
       <x:c r="A4" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D4" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E4" s="2">
         <x:v>3456789</x:v>
       </x:c>
       <x:c r="F4" s="2" t="s">
-        <x:v>111</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H4" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I4" s="2">
         <x:v>3456789</x:v>
@@ -1142,28 +1142,28 @@
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D5" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E5" s="2">
         <x:v>4567890</x:v>
       </x:c>
       <x:c r="F5" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H5" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="I5" s="2">
         <x:v>4567890</x:v>
@@ -1174,28 +1174,28 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D6" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E6" s="2">
         <x:v>5678901</x:v>
       </x:c>
       <x:c r="F6" s="2" t="s">
-        <x:v>117</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H6" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I6" s="2">
         <x:v>5678901</x:v>
@@ -1209,28 +1209,28 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E7" s="2">
         <x:v>6789012</x:v>
       </x:c>
       <x:c r="F7" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H7" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I7" s="2">
         <x:v>6789012</x:v>
@@ -1239,30 +1239,30 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:10">
+    <x:row r="8" spans="1:10" ht="32.75">
       <x:c r="A8" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>119</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E8" s="2">
         <x:v>7890123</x:v>
       </x:c>
       <x:c r="F8" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H8" s="2" t="s">
-        <x:v>119</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="I8" s="2">
         <x:v>7890123</x:v>
@@ -1273,28 +1273,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E9" s="2">
         <x:v>8901234</x:v>
       </x:c>
       <x:c r="F9" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H9" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="I9" s="2">
         <x:v>8901234</x:v>
@@ -1305,28 +1305,28 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>120</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E10" s="2">
         <x:v>9012345</x:v>
       </x:c>
       <x:c r="F10" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H10" s="2" t="s">
-        <x:v>120</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="I10" s="2">
         <x:v>9012345</x:v>
@@ -1340,28 +1340,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>116</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E11" s="2">
         <x:v>1234567</x:v>
       </x:c>
       <x:c r="F11" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H11" s="2" t="s">
-        <x:v>116</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I11" s="2">
         <x:v>1234567</x:v>
@@ -1372,28 +1372,28 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="2">
         <x:v>2345678</x:v>
       </x:c>
       <x:c r="F12" s="2" t="s">
-        <x:v>129</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G12" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H12" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I12" s="2">
         <x:v>2345678</x:v>
@@ -1407,28 +1407,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E13" s="2">
         <x:v>3456789</x:v>
       </x:c>
       <x:c r="F13" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G13" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H13" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I13" s="2">
         <x:v>3456789</x:v>
@@ -1437,30 +1437,30 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:10">
+    <x:row r="14" spans="1:10" ht="32.75">
       <x:c r="A14" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E14" s="2">
         <x:v>4567890</x:v>
       </x:c>
       <x:c r="F14" s="2" t="s">
-        <x:v>118</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G14" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H14" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I14" s="2">
         <x:v>4567890</x:v>
@@ -1471,28 +1471,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E15" s="2">
         <x:v>5678901</x:v>
       </x:c>
       <x:c r="F15" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G15" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H15" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I15" s="2">
         <x:v>5678901</x:v>
@@ -1503,28 +1503,28 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E16" s="2">
         <x:v>6789012</x:v>
       </x:c>
       <x:c r="F16" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H16" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I16" s="2">
         <x:v>6789012</x:v>
@@ -1538,28 +1538,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="2" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B17" s="2" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B17" s="2" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>136</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E17" s="2">
         <x:v>7890123</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H17" s="2" t="s">
-        <x:v>136</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I17" s="2">
         <x:v>7890123</x:v>
@@ -1568,30 +1568,30 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:10">
+    <x:row r="18" spans="1:10" ht="32.75">
       <x:c r="A18" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C18" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E18" s="2">
         <x:v>8901234</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>117</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H18" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I18" s="2">
         <x:v>8901234</x:v>
@@ -1602,28 +1602,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C19" s="2" t="s">
-        <x:v>143</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E19" s="2">
         <x:v>9012345</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H19" s="2" t="s">
-        <x:v>143</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I19" s="2">
         <x:v>9012345</x:v>
@@ -1634,28 +1634,28 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C20" s="2" t="s">
-        <x:v>140</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E20" s="2">
         <x:v>1234567</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
-        <x:v>144</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H20" s="2" t="s">
-        <x:v>140</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I20" s="2">
         <x:v>1234567</x:v>
@@ -1669,28 +1669,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C21" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E21" s="2">
         <x:v>2345678</x:v>
       </x:c>
       <x:c r="F21" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H21" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I21" s="2">
         <x:v>2345678</x:v>
@@ -1701,28 +1701,28 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C22" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D22" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E22" s="2">
         <x:v>3456789</x:v>
       </x:c>
       <x:c r="F22" s="2" t="s">
-        <x:v>129</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H22" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I22" s="2">
         <x:v>3456789</x:v>
@@ -1736,28 +1736,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C23" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E23" s="2">
         <x:v>4567890</x:v>
       </x:c>
       <x:c r="F23" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H23" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I23" s="2">
         <x:v>4567890</x:v>
@@ -1766,30 +1766,30 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:10">
+    <x:row r="24" spans="1:10" ht="32.75">
       <x:c r="A24" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C24" s="2" t="s">
-        <x:v>157</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D24" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E24" s="2">
         <x:v>5678901</x:v>
       </x:c>
       <x:c r="F24" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G24" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H24" s="2" t="s">
-        <x:v>157</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I24" s="2">
         <x:v>5678901</x:v>
@@ -1800,28 +1800,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C25" s="2" t="s">
-        <x:v>161</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D25" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E25" s="2">
         <x:v>6789012</x:v>
       </x:c>
       <x:c r="F25" s="2" t="s">
-        <x:v>160</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G25" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H25" s="2" t="s">
-        <x:v>161</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="I25" s="2">
         <x:v>6789012</x:v>
@@ -1832,28 +1832,28 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C26" s="2" t="s">
-        <x:v>151</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D26" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E26" s="2">
         <x:v>7890123</x:v>
       </x:c>
       <x:c r="F26" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G26" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H26" s="2" t="s">
-        <x:v>151</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I26" s="2">
         <x:v>7890123</x:v>
@@ -1867,28 +1867,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C27" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D27" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E27" s="2">
         <x:v>8901234</x:v>
       </x:c>
       <x:c r="F27" s="2" t="s">
-        <x:v>165</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G27" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H27" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I27" s="2">
         <x:v>8901234</x:v>
@@ -1899,28 +1899,28 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
-        <x:v>164</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D28" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E28" s="2">
         <x:v>9012345</x:v>
       </x:c>
       <x:c r="F28" s="2" t="s">
-        <x:v>111</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G28" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H28" s="2" t="s">
-        <x:v>164</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="I28" s="2">
         <x:v>9012345</x:v>
@@ -1934,28 +1934,28 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B29" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
-        <x:v>166</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D29" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E29" s="2">
         <x:v>1234567</x:v>
       </x:c>
       <x:c r="F29" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G29" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H29" s="2" t="s">
-        <x:v>166</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I29" s="2">
         <x:v>1234567</x:v>
@@ -1964,30 +1964,30 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:10">
+    <x:row r="30" spans="1:10" ht="32.75">
       <x:c r="A30" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C30" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D30" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E30" s="2">
         <x:v>2345678</x:v>
       </x:c>
       <x:c r="F30" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G30" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H30" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I30" s="2">
         <x:v>2345678</x:v>
@@ -1998,28 +1998,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C31" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D31" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E31" s="2">
         <x:v>3456789</x:v>
       </x:c>
       <x:c r="F31" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G31" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H31" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I31" s="2">
         <x:v>3456789</x:v>
@@ -2030,28 +2030,28 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C32" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D32" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E32" s="2">
         <x:v>4567890</x:v>
       </x:c>
       <x:c r="F32" s="2" t="s">
-        <x:v>118</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G32" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H32" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="I32" s="2">
         <x:v>4567890</x:v>
@@ -2065,28 +2065,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C33" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D33" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E33" s="2">
         <x:v>5678901</x:v>
       </x:c>
       <x:c r="F33" s="2" t="s">
-        <x:v>144</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G33" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H33" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I33" s="2">
         <x:v>5678901</x:v>
@@ -2095,30 +2095,30 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:10">
+    <x:row r="34" spans="1:10" ht="32.75">
       <x:c r="A34" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B34" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C34" s="2" t="s">
-        <x:v>99</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D34" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E34" s="2">
         <x:v>6789012</x:v>
       </x:c>
       <x:c r="F34" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G34" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H34" s="2" t="s">
-        <x:v>99</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I34" s="2">
         <x:v>6789012</x:v>
@@ -2129,28 +2129,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B35" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C35" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E35" s="2">
         <x:v>7890123</x:v>
       </x:c>
       <x:c r="F35" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G35" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H35" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I35" s="2">
         <x:v>7890123</x:v>
@@ -2161,28 +2161,28 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B36" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C36" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E36" s="2">
         <x:v>8901234</x:v>
       </x:c>
       <x:c r="F36" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G36" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H36" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="I36" s="2">
         <x:v>8901234</x:v>
@@ -2196,28 +2196,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B37" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C37" s="2" t="s">
-        <x:v>155</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D37" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E37" s="2">
         <x:v>9012345</x:v>
       </x:c>
       <x:c r="F37" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G37" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H37" s="2" t="s">
-        <x:v>155</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="I37" s="2">
         <x:v>9012345</x:v>
@@ -2226,30 +2226,30 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:10">
+    <x:row r="38" spans="1:10" ht="32.75">
       <x:c r="A38" s="2" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B38" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C38" s="2" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B38" s="2" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C38" s="2" t="s">
-        <x:v>141</x:v>
-      </x:c>
       <x:c r="D38" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E38" s="2">
         <x:v>1234567</x:v>
       </x:c>
       <x:c r="F38" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G38" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H38" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="I38" s="2">
         <x:v>1234567</x:v>
@@ -2260,28 +2260,28 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C39" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D39" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E39" s="2">
         <x:v>2345678</x:v>
       </x:c>
       <x:c r="F39" s="2" t="s">
-        <x:v>117</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G39" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H39" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="I39" s="2">
         <x:v>2345678</x:v>
@@ -2292,28 +2292,28 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B40" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C40" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D40" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E40" s="2">
         <x:v>3456789</x:v>
       </x:c>
       <x:c r="F40" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G40" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H40" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I40" s="2">
         <x:v>3456789</x:v>
@@ -2327,28 +2327,28 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B41" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C41" s="2" t="s">
-        <x:v>162</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D41" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E41" s="2">
         <x:v>4567890</x:v>
       </x:c>
       <x:c r="F41" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G41" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H41" s="2" t="s">
-        <x:v>162</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I41" s="2">
         <x:v>4567890</x:v>
@@ -2359,28 +2359,28 @@
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B42" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="2" t="s">
-        <x:v>154</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D42" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E42" s="2">
         <x:v>5678901</x:v>
       </x:c>
       <x:c r="F42" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G42" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H42" s="2" t="s">
-        <x:v>154</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I42" s="2">
         <x:v>5678901</x:v>
@@ -2394,28 +2394,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B43" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C43" s="2" t="s">
-        <x:v>147</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D43" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E43" s="2">
         <x:v>6789012</x:v>
       </x:c>
       <x:c r="F43" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G43" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H43" s="2" t="s">
-        <x:v>147</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I43" s="2">
         <x:v>6789012</x:v>
@@ -2424,30 +2424,30 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:10">
+    <x:row r="44" spans="1:10" ht="32.75">
       <x:c r="A44" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B44" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C44" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D44" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E44" s="2">
         <x:v>7890123</x:v>
       </x:c>
       <x:c r="F44" s="2" t="s">
-        <x:v>160</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G44" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H44" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="I44" s="2">
         <x:v>7890123</x:v>
@@ -2458,28 +2458,28 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B45" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C45" s="2" t="s">
-        <x:v>142</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D45" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E45" s="2">
         <x:v>8901234</x:v>
       </x:c>
       <x:c r="F45" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G45" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H45" s="2" t="s">
-        <x:v>142</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I45" s="2">
         <x:v>8901234</x:v>
@@ -2490,28 +2490,28 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B46" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C46" s="2" t="s">
-        <x:v>156</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D46" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E46" s="2">
         <x:v>9012345</x:v>
       </x:c>
       <x:c r="F46" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G46" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H46" s="2" t="s">
-        <x:v>156</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I46" s="2">
         <x:v>9012345</x:v>
@@ -2525,7 +2525,7 @@
     </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:K46"/>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
   <x:legacyDrawing r:id="rId1"/>
